--- a/CBT_策略库.xlsx
+++ b/CBT_策略库.xlsx
@@ -49,76 +49,76 @@
     <t>过度概括</t>
   </si>
   <si>
-    <t>“总是”、“从不”、“所有人都”、“每次都失败”、“永远”</t>
+    <t>"总是","从不","所有人都","每次都失败","永远"</t>
   </si>
   <si>
     <t>寻找反例</t>
   </si>
   <si>
-    <t>“有没有一次例外的情况？”、“你能否想到一个相反的例子？”</t>
-  </si>
-  <si>
-    <t>沮丧、无助感</t>
+    <t>"有没有一次例外的情况？","你能否想到一个相反的例子？"</t>
+  </si>
+  <si>
+    <t>沮丧,无助感</t>
   </si>
   <si>
     <t>灾难化</t>
   </si>
   <si>
-    <t>“完了”、“糟透了”、“后果不堪设想”、“无法忍受”</t>
+    <t>"完了","糟透了","后果不堪设想","无法忍受"</t>
   </si>
   <si>
     <t>可能性评估</t>
   </si>
   <si>
-    <t>“最坏的结果是什么？最好的呢？最现实的结果又可能是什么？”</t>
-  </si>
-  <si>
-    <t>焦虑、恐慌</t>
+    <t>"最坏的结果是什么？最好的呢？最现实的结果又可能是什么？"</t>
+  </si>
+  <si>
+    <t>焦虑,恐慌</t>
   </si>
   <si>
     <t>非黑即白</t>
   </si>
   <si>
-    <t>“要么成功要么失败”、“不是好人就是坏人”、“必须完美”</t>
+    <t>"要么成功要么失败","不是好人就是坏人","必须完美"</t>
   </si>
   <si>
     <t>连续谱技术</t>
   </si>
   <si>
-    <t>“如果0分是完全失败，10分是完全成功，你这次的事情可以打几分？为什么？”</t>
-  </si>
-  <si>
-    <t>压力、自我苛责</t>
+    <t>"如果0分是完全失败，10分是完全成功，你这次的事情可以打几分？为什么？"</t>
+  </si>
+  <si>
+    <t>压力,自我苛责</t>
   </si>
   <si>
     <t>以偏概全</t>
   </si>
   <si>
-    <t>“因为这一点否定全部”、“就因为这一件事”</t>
+    <t>"因为这一点否定全部","就因为这一件事"</t>
   </si>
   <si>
     <t>全面评估</t>
   </si>
   <si>
-    <t>“除了这个负面方面，整个事情/这个人还有其他特质吗？”</t>
-  </si>
-  <si>
-    <t>愤怒、失望</t>
+    <t>"除了这个负面方面，整个事情/这个人还有其他特质吗？"</t>
+  </si>
+  <si>
+    <t>愤怒,失望</t>
   </si>
   <si>
     <t>应该陈述</t>
   </si>
   <si>
-    <t xml:space="preserve">“我应该…”、“我必须…”、“他必须…” </t>
+    <t xml:space="preserve">"我应该…","我必须…","他必须…" </t>
   </si>
   <si>
     <t>成本效益分析</t>
   </si>
   <si>
-    <t>“持有这个‘应该’的想法，对你有什么好处和坏处？”</t>
-  </si>
-  <si>
-    <t>内疚、压力</t>
+    <t>"持有这个‘应该’的想法，对你有什么好处和坏处？"</t>
+  </si>
+  <si>
+    <t>内疚,压力</t>
   </si>
 </sst>
 </file>
